--- a/tally_workflow_query_spec_v2.xlsx
+++ b/tally_workflow_query_spec_v2.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -61,8 +61,20 @@
       <family val="0"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -87,8 +99,50 @@
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD966"/>
+        <bgColor rgb="00FFD966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF6347"/>
+        <bgColor rgb="00FF6347"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+        <bgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -96,6 +150,12 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -107,7 +167,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -155,6 +215,66 @@
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -410,214 +530,640 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="32" customWidth="1" style="8" min="1" max="1"/>
     <col width="110" customWidth="1" style="8" min="2" max="2"/>
+    <col width="75" customWidth="1" style="9" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1" s="9">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>Workflow Name</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="25" t="inlineStr">
         <is>
           <t>Query</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="75" customHeight="1" s="9">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
+        <is>
+          <t>FIELDS TO ADD TO THE QUERY (for 100% Tally Data Coverage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="55" customHeight="1" s="9">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>01 - Tally Company Sync</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>Get all active companies configured in Tally. For each company: company name, registered address, GSTIN, financial year start date, currency symbol (INR), contact person, phone, email, tin number, vat number, cst number. Filters: active companies only. Raw listing; no calculation. POST-SYNC: Write completion timestamp to SyncLog (WorkflowID='01-Company', Status='success', RecordsSynced=count).</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="75" customHeight="1" s="9">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="C2" s="29" t="inlineStr">
+        <is>
+          <t>CompanyID, CreatedAt, UpdatedAt</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="55" customHeight="1" s="9">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>02 - Tally Ledger Sync</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>Get all ledger accounts with their group classification and opening balances. For each ledger: ledger name, parent group name, group type (Asset/Liability/Income/Expense), opening balance inr, is-system-ledger flag, nature of group, under group name. Filters: all ledgers for selected company, current financial year. Raw listing; no calculation. POST-SYNC: Write completion timestamp to SyncLog.</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="75" customHeight="1" s="9">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
+        <is>
+          <t>LedgerID, CompanyID, GroupID, ClosingBalance, IsActive, StatementType, Nature, CreatedDate, LastModifiedDate</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="55" customHeight="1" s="9">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>03 - Tally Party Sync</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>Get all parties (customers and suppliers) with contact details and credit terms. For each party: party name, party type (Sundry Debtor/Sundry Creditor), parent group name, contact person, phone number, email, full address, city (parsed from address field or separate Tally field), state (derived from GSTIN first 2 digits mapped to state name), pincode (parsed from address), GSTIN, PAN, opening balance inr, credit limit inr, credit days, income tax number. Filters: ledgers under Sundry Debtors and Sundry Creditors groups. Raw listing; no calculation. POST-SYNC: Write completion timestamp to SyncLog.</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="75" customHeight="1" s="9">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
+        <is>
+          <t>PartyID, CompanyID, PAN, creditLimit, creditDays, salesPerson, city, state, PIN, openingBalance, Status, CreatedAt, UpdatedAt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="55" customHeight="1" s="9">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>04 - Tally Cash/Bank Sync</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>Get all cash-in-hand and bank account ledgers with current balances. For each account: ledger name, group name (Cash-in-Hand/Bank Accounts/Bank OD), current balance inr, bank account number, bank name, branch name, IFSC code, account type (Savings/Current/OD), last transaction date. Filters: ledgers under Cash-in-Hand, Bank Accounts, Bank OD groups. Raw listing; no calculation. POST-SYNC: Write completion timestamp to SyncLog.</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="75" customHeight="1" s="9">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
+        <is>
+          <t>AccountID, CompanyID, LedgerID, bankName, IFSC, branchName, accountType, IsActive, Location, lastSyncDate, CreatedAt, UpdatedAt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="55" customHeight="1" s="9">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>05 - Tally Sales Voucher Sync</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Get all sales vouchers with line item details. For each voucher header: voucher number, voucher date, voucher type (Sales/Sales Order), party name, party ID (mapped from Parties sheet), reference number, narration, gross total inr, total gst inr, round off inr, net amount inr, is-cancelled flag, sales person (from Cost Center or custom field if available in Tally, else null). For each line item: item ID (mapped from Items sheet), item name, stock item name, quantity, unit, rate per unit, amount inr, gst rate percent, gst amount inr, ledger name, debit amount, credit amount, sort order. Filters: VoucherType = Sales, date range (parameterized, default current financial year). Raw listing; no aggregation. POST-SYNC: Write completion timestamp to SyncLog.</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="75" customHeight="1" s="9">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
+        <is>
+          <t>VoucherID, CompanyID, grossTotal, totalGST, roundOff, netAmount, narration, referenceNo, salesPerson, isCancelled, SubTotal, LineID, LineType, CreatedDate, LastModifiedDate | LINE ITEM: ItemID, itemName, stockItemName, qty, unit, rate, amount, gstRate%, gstAmount, ledgerName, debitAmount, creditAmount, sortOrder</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="55" customHeight="1" s="9">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>06 - Tally Purchase Voucher Sync</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>Get all purchase vouchers with line item details. For each voucher header: voucher number, voucher date, voucher type (Purchase/Purchase Order), party name, party ID (mapped from Parties sheet), reference number, narration, gross total inr, total gst inr, round off inr, net amount inr, is-cancelled flag. For each line item: item ID (mapped from Items sheet), item name, stock item name, quantity, unit, rate per unit, amount inr, gst rate percent, gst amount inr, ledger name, debit amount, credit amount, sort order. Filters: VoucherType = Purchase, date range (parameterized). Raw listing; no aggregation. POST-SYNC: Write completion timestamp to SyncLog.</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="75" customHeight="1" s="9">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>VoucherID, CompanyID, grossTotal, totalGST, roundOff, netAmount, narration, referenceNo, isCancelled, taxableAmount, SubTotal, LineID, LineType, CreatedDate, LastModifiedDate | LINE ITEM: ItemID, itemName, qty, unit, rate, amount, gstRate, gstAmount, ledgerName, debit, credit, sortOrder</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="55" customHeight="1" s="9">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>07 - Tally Receipt/Payment Sync</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Get all receipt and payment vouchers. For each voucher header: voucher number, voucher date, voucher type (Receipt/Payment), party name, party ID (mapped from Parties sheet), reference number, narration, total amount inr, is-cancelled flag. For each line item: ledger name, ledger ID, debit amount inr, credit amount inr, sort order. Filters: VoucherType in (Receipt, Payment), date range (parameterized). Raw listing; no aggregation. POST-SYNC: Write completion timestamp to SyncLog.</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="75" customHeight="1" s="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>VoucherID, CompanyID, referenceNo, narration, isCancelled, paymentMode, chequeNo, bankAccount, LineID, LineType, SubTotal, TaxAmount, CreatedDate, LastModifiedDate | LINE ITEM: ledgerName, ledgerID, debitAmount, creditAmount, sortOrder</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="55" customHeight="1" s="9">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>08 - Tally Adjustment Voucher Sync</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>Get all journal, debit note, and credit note vouchers with ledger entries. For each voucher header: voucher number, voucher date, voucher type (Journal/Debit Note/Credit Note), party name (if applicable), party ID (if applicable), reference number, narration, total amount inr, is-cancelled flag. For each line item: ledger name, ledger ID, debit amount inr, credit amount inr, narration, sort order. Filters: VoucherType in (Journal, Debit Note, Credit Note), date range (parameterized). Raw listing; no aggregation. POST-SYNC: Write completion timestamp to SyncLog.</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="75" customHeight="1" s="9">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>VoucherID, CompanyID, narration, referenceNo, isCancelled, LineID, LineType, CreatedDate, LastModifiedDate | LINE ITEM: ledgerName, ledgerID, debitAmount, creditAmount, narration, sortOrder | CREDIT/DEBIT NOTE: originalInvoiceReference, taxReversal, reason | EXPENSES: expenseType, notes, billReference</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="55" customHeight="1" s="9">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>09 - Tally Inventory Sync</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Get all stock items with stock groups and current stock position. For each stock group: group name, parent group name. For each stock item: item name, stock group name, category name, brand (from Tally stock item master if field exists, else derived from category prefix or null), HSN code, unit of measure, alternate unit, conversion factor, gst rate percent, sale rate inr, purchase rate inr, opening stock quantity, opening stock value inr, current stock quantity, current stock value inr, minimum order quantity, reorder level, standard cost, is-active flag. Filters: all stock items for selected company. Raw listing; no calculation beyond current stock position. POST-SYNC: Write completion timestamp to SyncLog. CRITICAL ISSUE: Workflow writes 17 columns but Items.csv has 22 columns (Brand, SubCategory, GroupID added manually). OVERWRITE mode will WIPE these columns on next daily sync at 02:00. FIX: Add Brand/SubCategory/GroupID to workflow transform code OR switch to UPSERT mode.</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="75" customHeight="1" s="9">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>ItemID, CompanyID, Brand, CategoryID, SubCategory, GroupID, MRP, MinStockLevel, MaxStockLevel, ReorderLevel, Location, HSN, IsActive, openingStock, purchaseRate, IsBatchTracked, CreatedDate, LastModifiedDate</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="55" customHeight="1" s="9">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>10 - Tally Outstanding Sync</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>Get receivables and payables aging reports. For each receivable entry: party name, party ID (mapped), bill reference, bill date, due date, bill amount inr, pending amount inr, days overdue (computed: today minus due date, 0 if not due), aging bucket (computed: 'Not Due' if days overdue &lt;=0, '0-30' if 1-30, '31-60' if 31-60, '61-90' if 61-90, '180+' if &gt;90). For each payable entry: same fields. Filters: all outstanding bills, as-of date (parameterized, default today). Include computed days overdue and aging bucket fields. POST-SYNC: Write completion timestamp to SyncLog.</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="75" customHeight="1" s="9">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>partyPhone, partyEmail, partyAddress, partyGSTIN, partyPAN, creditLimit, creditDays, salesPerson, city, state, PIN, openingBalance</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="55" customHeight="1" s="9">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>11 - Tally Dashboard Refresh</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Get dashboard summary metrics. For each metric: metric name (Cash in Hand, Bank Balance, Total Sales, Total Purchases, Receivables, Payables, Stock Value, GST Liability), current period value inr, previous period value inr, trend percent (computed: current minus previous divided by previous, null if previous is 0), trend direction (computed: 'up' if positive, 'down' if negative, 'flat' if zero or null). Filters: date range (parameterized, default current financial year to date), comparison period (parameterized, default previous equal-length period). Include computed trend fields. POST-SYNC: Write completion timestamp to SyncLog.</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="75" customHeight="1" s="9">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>itemCount, partyCount, topSellingItems, categoryBreakdown, openOrders, recentTransactions, salesTrend data, topCustomersList, topVendorsList, bankAccountDetails (IFSC, accountNo, branchName), pendingOrders, overdueAmount, stockSummary</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="55" customHeight="1" s="9">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>12 - Tally Reconciliation Sync</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>Get trial balance and bank statement data. For trial balance: ledger name, ledger ID, opening debit inr, opening credit inr, current period debit inr, current period credit inr, closing debit inr, closing credit inr. For bank statement: bank account name, bank ledger ID, transaction date, narration, reference number, debit amount inr, credit amount inr, running balance inr (computed: cumulative sum ordered by date). Filters: all ledgers for trial balance, date range (parameterized) for bank statement. Include computed running balance for bank statement. POST-SYNC: Write completion timestamp to SyncLog.</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="75" customHeight="1" s="9">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>groupNature, parentGroup, StatementType, comparativePeriod | PROFIT LOSS: detailedExpenseBreakdown, revenueStreams, otherIncome, depreciation, financeCosts, employeeCosts, detailedLedgerGroupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="55" customHeight="1" s="9">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>13 - Tally Stock Batch Sync</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Get batch-wise stock details for items with batch tracking enabled. For each batch: batch ID (Tally batch reference), item ID (mapped from Items sheet), item name, stock group name, godown/location, inward date, expiry date (if applicable), quantity received, quantity remaining, batch status (Active/Expired/Exhausted), unit cost inr, total value inr. Filters: all batches for selected company, items with batch tracking enabled. Raw listing. Note: Only runs if Tally batch tracking is confirmed enabled. POST-SYNC: Write completion timestamp to SyncLog. STATUS: NOT IMPLEMENTED - No workflow exists. Sheet populated once by generate_seed_data.py and going stale. REQUIRED: New workflow needed.</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="75" customHeight="1" s="9">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
+        <is>
+          <t>BatchID, CompanyID, ItemID, BatchNo, Quantity, InwardDate, MfgDate, ExpDate, Rate, Value, AgeingDays, AgeingBucket, Location, CreatedAt, UpdatedAt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="55" customHeight="1" s="9">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>14 - Customer Movement Rollup</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>Computed rollup (not a Tally pull). Reads Parties sheet and Sales Voucher headers. For each party where PartyType='Sundry Debtor': party ID, party name, city, state, last transaction date (max of SalesVoucherDate where PartyID matches), days since last transaction (computed: today minus last transaction date), status (computed: 'Active' if days &lt;= deadCustomerThreshold, else 'Dead'), aging bucket for dead (computed: '0-30' if 1-30 days dead, '31-60' if 31-60, '61-90' if 61-90, '180+' if &gt;90). Threshold for dead customer: configurable setting (default 90 days). Writes to CustomerMovement sheet. POST-SYNC: Write completion timestamp to SyncLog. STATUS: NOT IMPLEMENTED - No workflow exists. Sheet populated once by generate_seed_data.py and going stale. REQUIRED: New workflow needed.</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="75" customHeight="1" s="9">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
+        <is>
+          <t>MovementID, CompanyID, PartyID, PartyType, FirstTransactionDate, LastTransactionDate, TotalSalesValue, TotalPurchaseValue, TransactionCount, DaysSinceLastTxn, Status, SalesPerson, City, State</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="55" customHeight="1" s="9">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>15 - Item Stock Status Rollup</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>Computed rollup (not a Tally pull). Reads Items sheet and VoucherLines from Sales Vouchers. For each item: item ID, item name, category, stock group, brand, current stock quantity, reorder level, sales velocity (computed: total quantity sold in last 30 days divided by 30), understock flag (computed: current stock &lt; reorder level), overstock flag (computed: current stock &gt; sales velocity x overstockMultiplier, default multiplier 3), popular flag (computed: rank by total sales value last 30 days, top N where N is configurable setting default 10). Writes to ItemStockStatus sheet. POST-SYNC: Write completion timestamp to SyncLog. STATUS: NOT IMPLEMENTED - No workflow exists. Sheet populated once by generate_seed_data.py and going stale. REQUIRED: New workflow needed.</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="75" customHeight="1" s="9">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="C16" s="34" t="inlineStr">
+        <is>
+          <t>StatusID, CompanyID, ItemID, SalesVelocity30d, IsUnderstock, IsOverstock, IsPopular, DaysOfStock, StockValue, LastSaleDate, LastPurchaseDate</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="55" customHeight="1" s="9">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>16 - Geographic Rollup</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>Computed rollup (not a Tally pull). Reads Parties sheet, Sales Voucher totals, Purchase Voucher totals. Aggregates by state and city. For each state-city combination: state, city, customer count (distinct parties), total sales inr (sum of Sales vouchers), total purchases inr (sum of Purchase vouchers), net amount inr (sales minus purchases). Filters: company ID. Writes to GeographicSummary sheet. POST-SYNC: Write completion timestamp to SyncLog. STATUS: NOT IMPLEMENTED - No workflow exists. Sheet populated once by generate_seed_data.py and going stale. REQUIRED: New workflow needed.</t>
+        </is>
+      </c>
+      <c r="C17" s="34" t="inlineStr">
+        <is>
+          <t>GeoID, CompanyID, State, City, PartyCount, TotalSalesValue, TotalPurchaseValue, TotalOutstanding, TopCustomers, TopItems, PeriodStart, PeriodEnd</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="55" customHeight="1" s="9">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>17 - Tally GST Liability Sync</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Get all GST tax liability ledgers with ITC and output tax breakdown. For each tax ledger: ledger name, net tax liability inr, inward ITC inr, outward tax inr, GSTIN, period (month/year), return filing status, payment status, due date. Filters: all GST-related ledgers for selected company. Raw listing. POST-SYNC: Write completion timestamp to SyncLog.</t>
+        </is>
+      </c>
+      <c r="C18" s="33" t="inlineStr">
+        <is>
+          <t>ledgerDetails, period, returnFilingStatus, paymentStatus, dueDate, GSTIN, LedgerID, CompanyID</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="55" customHeight="1" s="9">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>18 - Tally Party Ledger Statement</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>Get detailed ledger transaction statement for a given party or ledger. For each transaction: date, voucher number, voucher type, particulars (party name or ledger name), debit amount inr, credit amount inr, closing balance inr. Filters: specified party name or ledger name (parameterized), date range (parameterized). Raw listing; no aggregation. POST-SYNC: N/A (on-demand query).</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>openingBalance, closingBalance, groupName, ledgerType, LedgerID</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="55" customHeight="1" s="9">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>19 - Tally Pending Orders Sync</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>Get all pending sales orders with item-level dispatch status. For each order: order number, order date, party name, total amount inr, dispatch status, due date, items (comma-separated list), ordered quantity, dispatched quantity, pending quantity, reference number, expected delivery date, narration. Filters: VoucherType = Sales Order, status = pending or partially dispatched. Raw listing; no aggregation. POST-SYNC: Write completion timestamp to SyncLog.</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>OrderID, PartyID, referenceNo, itemID, rate, narration, expectedDate</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="80" customHeight="1" s="9">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>20 - Item Wise &amp; Party Wise Sales</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>Get sales voucher line items with item details aggregated by item and by party. For item-wise: itemID, itemName, Brand, Unit, SaleRate, GST, HSN, totalQty, totalAmount, voucherCount, lastSaleDate. For party-wise: PartyID, PartyName, totalSalesAmount, voucherCount, lastVoucherDate, VoucherType. Filters: VoucherType = Sales, date range (parameterized, default current financial year). POST-SYNC: Write completion timestamp to SyncLog.</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>ItemID, itemName, Brand, Unit, SaleRate, GST, HSN, totalQty, totalAmount, voucherCount, lastSaleDate | PARTY: PartyID, PartyName, totalSalesAmount, voucherCount, lastVoucherDate, VoucherType</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="80" customHeight="1" s="9">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>21 - Receipt Note Vouchers</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>Get all receipt note vouchers with party details. For each voucher: VoucherNo, VoucherDate, PartyID, PartyName, GrandTotal, Narration, Status, VoucherType, referenceNo. Filters: VoucherType = Receipt Note, date range (parameterized). POST-SYNC: Write completion timestamp to SyncLog.</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>VoucherID, CompanyID, VoucherNo, VoucherDate, PartyID, PartyName, GrandTotal, Narration, Status, VoucherType, referenceNo, CreatedDate, LastModifiedDate</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="80" customHeight="1" s="9">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>22 - Delivery Note Vouchers</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>Get all delivery note vouchers with party details. For each voucher: VoucherNo, VoucherDate, PartyID, PartyName, GrandTotal, Narration, Status, VoucherType, referenceNo. Filters: VoucherType = Delivery Note, date range (parameterized). POST-SYNC: Write completion timestamp to SyncLog.</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>VoucherID, CompanyID, VoucherNo, VoucherDate, PartyID, PartyName, GrandTotal, Narration, Status, VoucherType, referenceNo, CreatedDate, LastModifiedDate</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="80" customHeight="1" s="9">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>23 - Contra Vouchers</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>Get all contra vouchers with bank and cash account details. For each voucher: VoucherNo, VoucherDate, GrandTotal, Narration, Status, VoucherType, fromAccount, toAccount, fromBankName, toBankName, fromAccountNo, toAccountNo. For each line item: ledgerName, ledgerID, debitAmount, creditAmount. Filters: VoucherType = Contra, date range (parameterized). POST-SYNC: Write completion timestamp to SyncLog.</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>VoucherID, CompanyID, VoucherNo, VoucherDate, GrandTotal, Narration, Status, fromAccount, toAccount, fromBankName, toBankName, fromAccountNo, toAccountNo | LINE ITEM: ledgerName, ledgerID, debitAmount, creditAmount</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="80" customHeight="1" s="9">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>24 - Top Brands Report</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>Get sales data aggregated by brand with stock status. For each brand: Brand, totalSalesAmount, totalQtySold, itemCount, topItem, stockAvailability, salesVelocity30d. Computed from sales voucher line items joined with Items and ItemStockStatus. Filters: date range (parameterized, default current financial year). POST-SYNC: Write completion timestamp to SyncLog.</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>Brand, ItemID, ItemName, SaleRate, CurrentStock, SalesVelocity30d, totalQtySold, totalSalesAmount, voucherCount, lastSaleDate</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="80" customHeight="1" s="9">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>25 - Top Report (Top Customers/Vendors/Products)</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>Get top performing customers, vendors, and products by total value. For each entity: name/PartyName, totalValue, transactionCount, percentage of total. Top customers from Sales vouchers, top vendors from Purchase vouchers, top products from Sales voucher lines. Filters: date range (parameterized), top N (default 10). POST-SYNC: Write completion timestamp to SyncLog.</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>PartyID, PartyName, PartyType, totalValue, transactionCount, percentageOfTotal, rankingPosition, VoucherType, VoucherDate range</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="80" customHeight="1" s="9">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>26 - By Ledger Report</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>Get voucher line items grouped by ledger with related voucher details. For each entry: LedgerID, LedgerName, GroupName, totalAmount, voucherCount, VoucherNo, VoucherDate, VoucherType, debitTotal, creditTotal. Computed from VoucherLines joined with Vouchers, Ledgers, and Groups. Filters: date range (parameterized). POST-SYNC: Write completion timestamp to SyncLog.</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>LedgerID, LedgerName, GroupID, GroupName, totalAmount, totalDebit, totalCredit, voucherCount, VoucherNo, VoucherDate, VoucherType</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="80" customHeight="1" s="9">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>27 - Ledger Report (Summary)</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>Get ledger summary with opening and closing balances and total transactions. For each ledger: LedgerID, LedgerName, GroupID, GroupName, OpeningBalance, ClosingBalance, totalDebit, totalCredit, netMovement, voucherCount, lastVoucherDate. Filters: all ledgers for selected company, current financial year. POST-SYNC: Write completion timestamp to SyncLog.</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>LedgerID, LedgerName, GroupID, GroupName, OpeningBalance, ClosingBalance, totalDebit, totalCredit, netMovement, voucherCount, lastVoucherDate</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="80" customHeight="1" s="9">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>28 - Ledger Detail (Full)</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>Get full ledger detail including bank and cash account information for bank/cash ledgers. For each ledger: LedgerID, LedgerName, GroupName, OpeningBalance, ClosingBalance, totalDebit, totalCredit, IsActive, Nature. For bank/cash ledgers additionally: AccountNumber, BankName, IFSC, BranchName. Filters: all ledgers for selected company. POST-SYNC: Write completion timestamp to SyncLog.</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>LedgerID, CompanyID, LedgerName, GroupID, GroupName, OpeningBalance, ClosingBalance, totalDebit, totalCredit, IsActive, Nature, AccountNumber, BankName, IFSC, BranchName, Location</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="80" customHeight="1" s="9">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>29 - Groups Master</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>Get group hierarchy with classification details. For each group: GroupID, GroupName, ParentGroup, GroupType, Nature, StatementType, childGroupCount, ledgerCount. Filters: all groups for selected company. POST-SYNC: Write completion timestamp to SyncLog.</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>GroupID, CompanyID, GroupName, ParentGroup, GroupType, Nature, StatementType, childGroupCount, ledgerCount, CreatedDate, LastModifiedDate</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="80" customHeight="1" s="9">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>30 - Categories Master</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>Get item categories with associated item groups and item counts. For each category: CategoryID, CategoryName, Description. For each item group: GroupID, GroupName, CategoryID. For each item in group: ItemID, ItemName, OpeningStock, SaleRate. Filters: all categories and item groups for selected company. POST-SYNC: Write completion timestamp to SyncLog.</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>CategoryID, CategoryName, Description, GroupID, GroupName, ItemID, ItemName, OpeningStock, SaleRate, itemCount, CreatedAt, UpdatedAt</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="80" customHeight="1" s="9">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>31 - Items Page (Full Inventory)</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>Get all stock items with complete stock status and analytics. For each item: ItemID, ItemName, Brand, SaleRate, Unit, GST, CurrentStock, SalesVelocity30d, IsUnderstock, IsOverstock, IsPopular, DaysOfStock, ReorderLevel, StockValue, LastSaleDate, LastPurchaseDate, MinStockLevel, MaxStockLevel, Location, HSN, CategoryID, GroupID. Computed analytics from Template 9 (stock status) joined with Items master. Filters: all items for selected company. POST-SYNC: Write completion timestamp to SyncLog.</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>ItemID, ItemName, Brand, SaleRate, Unit, GST, CurrentStock, SalesVelocity30d, IsUnderstock, IsOverstock, IsPopular, DaysOfStock, ReorderLevel, StockValue, LastSaleDate, LastPurchaseDate, MinStockLevel, MaxStockLevel, Location, HSN, CategoryID, GroupID</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="80" customHeight="1" s="9">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>32 - Stock Batches</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>Get batch-wise stock details for items with batch tracking. For each batch: BatchID, BatchNo, ItemID, ItemName, Quantity, InwardDate, MfgDate, ExpDate, Rate, Value, AgeingDays, AgeingBucket, Location. Filters: all batches for selected company, items with batch tracking enabled. POST-SYNC: Write completion timestamp to SyncLog.</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>BatchID, CompanyID, ItemID, ItemName, BatchNo, Quantity, InwardDate, MfgDate, ExpDate, Rate, Value, AgeingDays, AgeingBucket, Location, CreatedAt, UpdatedAt</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="80" customHeight="1" s="9">
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>33 - Item Stock Status (Analytics)</t>
+        </is>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>Get computed stock analytics for all items. For each item: StatusID, ItemID, ItemName, CurrentStock, SalesVelocity30d, IsUnderstock, IsOverstock, IsPopular, DaysOfStock, ReorderLevel, StockValue, LastSaleDate, LastPurchaseDate. Computed from Sales VoucherLines (last 30 days for velocity) and Items master (reorder level, stock qty). Filters: all items for selected company. POST-SYNC: Write completion timestamp to SyncLog.</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>StatusID, CompanyID, ItemID, ItemName, CurrentStock, SalesVelocity30d, IsUnderstock, IsOverstock, IsPopular, DaysOfStock, ReorderLevel, StockValue, LastSaleDate, LastPurchaseDate</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="80" customHeight="1" s="9">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>34 - Geographic Summary</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>Get sales and purchase aggregation by state and city. For each state-city: State, City, PartyCount, TotalSalesValue, TotalPurchaseValue, TotalOutstanding, TopCustomers, TopItems, PeriodStart, PeriodEnd. Computed from Parties sheet joined with Sales and Purchase vouchers aggregated by PartyID city/state. Filters: selected company, date range (parameterized). POST-SYNC: Write completion timestamp to SyncLog.</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>GeoID, CompanyID, State, City, PartyCount, TotalSalesValue, TotalPurchaseValue, TotalOutstanding, TopCustomers, TopItems, PeriodStart, PeriodEnd, CreatedAt, UpdatedAt</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="80" customHeight="1" s="9">
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>35 - Customer Movement</t>
+        </is>
+      </c>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>Get customer movement analysis with first/last transaction dates and sales/purchase totals. For each customer: MovementID, PartyID, PartyName, PartyType, FirstTransactionDate, LastTransactionDate, TotalSalesValue, TotalPurchaseValue, TransactionCount, DaysSinceLastTxn, Status, SalesPerson, City, State. Computed from Parties joined with Sales and Purchase vouchers. Filters: PartyType = Customer, selected company. POST-SYNC: Write completion timestamp to SyncLog.</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>MovementID, CompanyID, PartyID, PartyName, PartyType, FirstTransactionDate, LastTransactionDate, TotalSalesValue, TotalPurchaseValue, TransactionCount, DaysSinceLastTxn, Status, SalesPerson, City, State</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="80" customHeight="1" s="9">
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>36 - Outstanding Group View</t>
+        </is>
+      </c>
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>Get outstanding receivables and payables grouped by ledger/party type with aging breakdown. For each group: groupType, PartyID, PartyName, totalOutstanding, agingNotDue, aging0to30, aging31to60, aging61to90, aging90plus, creditLimit, creditDays, OpeningBalance. Computed from Outstanding templates (2,3,4,7,32,34,35,37,41,42) joined with Parties and Ledgers. Filters: selected company. POST-SYNC: Write completion timestamp to SyncLog.</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>PartyID, PartyName, PartyType, groupType, totalOutstanding, agingNotDue, aging0to30, aging31to60, aging61to90, aging90plus, creditLimit, creditDays, OpeningBalance, City, State</t>
         </is>
       </c>
     </row>
